--- a/Data/EXCEL/Transfer/bzPerformance/20250413PAP/2882-bzPerformance_perAndPbr20250413PAP.xlsx
+++ b/Data/EXCEL/Transfer/bzPerformance/20250413PAP/2882-bzPerformance_perAndPbr20250413PAP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20250413PAP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\20250413PAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55154463-46A1-49D1-B5B6-65D074C44E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5EB4CE3A-6798-4329-834F-6B3C7692F138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" xr2:uid="{952218AE-A9A6-4C74-9598-3772F709192B}"/>
+    <workbookView xWindow="1800" yWindow="840" windowWidth="17640" windowHeight="14310" xr2:uid="{5A045B35-2C90-450E-940C-6AFF62E2AC6B}"/>
   </bookViews>
   <sheets>
     <sheet name="2882-bzPerformance_perAndPbr202" sheetId="2" r:id="rId1"/>
@@ -1267,23 +1267,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA8EC31E-7144-4590-9929-57F7166700BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{033CD4E7-7BB8-4361-8713-3FD3BB14D589}">
   <dimension ref="A1:Q38"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="3" width="11.6640625" customWidth="1"/>
-    <col min="4" max="6" width="12.109375" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" customWidth="1"/>
-    <col min="9" max="9" width="11.6640625" customWidth="1"/>
-    <col min="10" max="10" width="12.109375" customWidth="1"/>
-    <col min="11" max="13" width="11.6640625" customWidth="1"/>
-    <col min="14" max="14" width="12.109375" customWidth="1"/>
-    <col min="15" max="16" width="11.6640625" customWidth="1"/>
-    <col min="17" max="17" width="12.44140625" customWidth="1"/>
+    <col min="1" max="3" width="8.54296875" customWidth="1"/>
+    <col min="4" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="8.54296875" customWidth="1"/>
+    <col min="8" max="8" width="9.90625" customWidth="1"/>
+    <col min="9" max="9" width="8.54296875" customWidth="1"/>
+    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="11" max="13" width="8.54296875" customWidth="1"/>
+    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="15" max="16" width="8.54296875" customWidth="1"/>
+    <col min="17" max="17" width="9.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1314,7 +1314,7 @@
       <c r="P1" s="21"/>
       <c r="Q1" s="22"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A2" s="18"/>
       <c r="B2" s="4" t="s">
         <v>2</v>
@@ -1365,7 +1365,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="19"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1402,7 +1402,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A4" s="6">
         <v>2025</v>
       </c>
@@ -1455,7 +1455,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A5" s="10">
         <v>2024</v>
       </c>
@@ -1508,7 +1508,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
         <v>2023</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A7" s="10">
         <v>2022</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A8" s="6">
         <v>2021</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A9" s="10">
         <v>2020</v>
       </c>
@@ -1720,7 +1720,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A10" s="6">
         <v>2019</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A11" s="10">
         <v>2018</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A12" s="6">
         <v>2017</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A13" s="10">
         <v>2016</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A14" s="6">
         <v>2015</v>
       </c>
@@ -1985,7 +1985,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A15" s="10">
         <v>2014</v>
       </c>
@@ -2038,7 +2038,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A16" s="6">
         <v>2013</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A17" s="10">
         <v>2012</v>
       </c>
@@ -2144,7 +2144,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A18" s="6">
         <v>2011</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A19" s="10">
         <v>2010</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>2.3199999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A20" s="6">
         <v>2009</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A21" s="10">
         <v>2008</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A22" s="6">
         <v>2007</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A23" s="10">
         <v>2006</v>
       </c>
@@ -2462,7 +2462,7 @@
         <v>2.81</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A24" s="6">
         <v>2005</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A25" s="10">
         <v>2004</v>
       </c>
@@ -2568,7 +2568,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A26" s="6">
         <v>2003</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>2.57</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A27" s="10">
         <v>2002</v>
       </c>
@@ -2674,7 +2674,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A28" s="6">
         <v>2001</v>
       </c>
@@ -2727,7 +2727,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A29" s="10">
         <v>2000</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A30" s="6">
         <v>1999</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A31" s="10">
         <v>1998</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A32" s="6">
         <v>1997</v>
       </c>
@@ -2939,7 +2939,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A33" s="10">
         <v>1996</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A34" s="6">
         <v>1995</v>
       </c>
@@ -3045,7 +3045,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A35" s="10">
         <v>1994</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A36" s="6">
         <v>1993</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A37" s="10">
         <v>1992</v>
       </c>
@@ -3204,7 +3204,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A38" s="6">
         <v>1991</v>
       </c>
